--- a/pharmacy_forms/045_rx_refills--pharmacy_forms.xlsx
+++ b/pharmacy_forms/045_rx_refills--pharmacy_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -869,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>medical_history_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>medical history</t>
+          <t>Medical History 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>medical_record_number</t>
+          <t>medical_record_number_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>medical record number</t>
+          <t>Medical Record Number 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -992,12 +992,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>contact_number_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>contact number</t>
+          <t>Contact Number 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>medical_provider</t>
+          <t>medical_provider_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>medical provider</t>
+          <t>Medical Provider 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'value':_'option_1_value'}</t>
+          <t>option_1_value</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'value': 'option_1_value'}</t>
+          <t>option 1 value</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'value':_'option_2_value'}</t>
+          <t>option_2_value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'value': 'option_2_value'}</t>
+          <t>option 2 value</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'value':_'option_1_value'}</t>
+          <t>option_1_value</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'value': 'option_1_value'}</t>
+          <t>option 1 value</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'value':_'option_2_value'}</t>
+          <t>option_2_value</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'value': 'option_2_value'}</t>
+          <t>option 2 value</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'value':_'option_1_value'}</t>
+          <t>option_1_value</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'value': 'option_1_value'}</t>
+          <t>option 1 value</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'value':_'option_2_value'}</t>
+          <t>option_2_value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'value': 'option_2_value'}</t>
+          <t>option 2 value</t>
         </is>
       </c>
     </row>
